--- a/sheets_template/personal_sheet_sample.xlsx
+++ b/sheets_template/personal_sheet_sample.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,11 @@
           <t>fat_g</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -503,6 +508,9 @@
       <c r="G2" t="n">
         <v>20</v>
       </c>
+      <c r="H2" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -531,6 +539,9 @@
       </c>
       <c r="G3" t="n">
         <v>37</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
